--- a/data/20260915/產能參數檔案_GLD6_ProductionPlanning update 14.09.26.xlsx
+++ b/data/20260915/產能參數檔案_GLD6_ProductionPlanning update 14.09.26.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="B04_Capacity" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Production_Planning" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Holidays_Table" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="B01_Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B02_Summary_By _Order" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B04_Capacity_Three_of_Month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Production_Planning" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Holidays_Table" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="B01_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B02_Summary_By _Order" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1745,6 +1746,1711 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AL16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>9月 上旬</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>9月 中旬</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>9月 下旬</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>10月 上旬</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>10月 中旬</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>10月 下旬</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>11月 上旬</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>11月 中旬</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>11月 下旬</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>12月 上旬</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>12月 中旬</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>12月 下旬</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>1月 上旬</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>1月 中旬</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>1月 下旬</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2月 上旬</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2月 中旬</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2月 下旬</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>3月 上旬</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>3月 中旬</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>3月 下旬</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>4月 上旬</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>4月 中旬</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>4月 下旬</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>5月 上旬</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>5月 中旬</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>5月 下旬</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>6月 上旬</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>6月 中旬</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>6月 下旬</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>7月 上旬</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>7月 中旬</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>7月 下旬</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>8月 上旬</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>8月 中旬</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>8月 下旬</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>月份/Month</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9月Sep</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10月Oct</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11月Nov</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12月Dec</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1月Jan</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2月Feb</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3月Mar</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4月Apr</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>5月May</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>6月Jun</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>7月Jul</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>8月Aug</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>旬別</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>上旬</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>中旬</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>下旬</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>已排線產能
+Scheduled Capacity</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>16341.27583333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13567.89945775302</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17217.412786308</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17965.76346243</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15312.23262823798</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20687.23907468401</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17606.882866314</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18234.29799185402</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18121.15723408202</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18336.91841112599</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11224.680014016</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11606.35346282999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8589.558576857991</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7455.356248409997</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2109.408</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>20655.4175</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18984.1775</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>19385.79916666666</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>14076.3525</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>13504.395</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>11774.47166666667</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>未排線產能
+Unscheduled Capacity</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1696</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4770</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7314</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6360</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11766</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17384</v>
+      </c>
+      <c r="R5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="S5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12720</v>
+      </c>
+      <c r="U5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="V5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="W5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="X5" t="n">
+        <v>19080</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16960</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14840</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>總產能
+Total Capacity</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16341.27583333333</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13567.89945775302</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17217.412786308</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17965.76346243</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15312.23262823798</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20687.23907468401</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17606.882866314</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18234.29799185402</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18121.15723408202</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20032.91841112599</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15994.680014016</v>
+      </c>
+      <c r="N6" t="n">
+        <v>18920.35346283</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14949.55857685799</v>
+      </c>
+      <c r="P6" t="n">
+        <v>19221.35624841</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19493.408</v>
+      </c>
+      <c r="R6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="S6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12720</v>
+      </c>
+      <c r="U6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="V6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="X6" t="n">
+        <v>19080</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>16960</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14840</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>20655.4175</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18984.1775</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>19385.79916666666</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14076.3525</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>13504.395</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>11774.47166666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>預估產能
+Estimated Capacity</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>16727.27272727273</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12545.45454545454</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16727.27272727273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>17833.33333333333</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15851.85185185185</v>
+      </c>
+      <c r="H7" t="n">
+        <v>19814.81481481481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15840</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17820</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15840</v>
+      </c>
+      <c r="L7" t="n">
+        <v>17826.92307692308</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15846.15384615385</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17826.92307692308</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15789.47368421052</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13815.78947368421</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7894.736842105262</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17280</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17280</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19440</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>13847.82608695652</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15826.08695652174</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15826.08695652174</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>17333.33333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>17333.33333333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17333.33333333333</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19666.66666666666</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17481.48148148148</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>21851.85185185185</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>19075</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>19075</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>16350</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>出口總數
+Confirmed Order</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>23628.9233332</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5108.7066665</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6002.9408332</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19420.8358331</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18112.3849999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15552.5633332</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22273.6866664</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11458.0516666</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8323.877500000001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11280.9858333</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6769.3058333</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8157.7716666</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1334.305</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2328.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>排線效率
+Scheduled Efficiency</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.524095579247759</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.647527786745495</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.573609375555526</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.520577092020353</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.457153868189906</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.564360035889713</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.674479274302802</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.548772690425019</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.717360037369354</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.711715776571669</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.492469833953583</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.595685482605232</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.636206040441512</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.626751126901378</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.996400000000001</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="n">
+        <v>1.852597025653138</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.865773262826417</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.675250714690038</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.697652946073154</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.565020748920466</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.486099381393999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>排線人數
+Scheduled Sewers</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>36.53125</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36.79387966666668</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.88552800000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36.90601777777778</v>
+      </c>
+      <c r="G10" t="n">
+        <v>36.90402325000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>36.85446750000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>36.74946750000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>36.6395292777778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>36.62578700000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36.56214573170733</v>
+      </c>
+      <c r="M10" t="n">
+        <v>36.32641947826087</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36.21807297297298</v>
+      </c>
+      <c r="O10" t="n">
+        <v>36.26959337500001</v>
+      </c>
+      <c r="P10" t="n">
+        <v>36.71115202898552</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>36.0125</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>36.05625</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>36.565</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36.55714285714286</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>排線加班率
+Scheduled OT Rate</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.08992728731822068</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.108233624367477</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1015475627392393</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05675868586140913</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05742041502886863</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.06599205625478151</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.06252693729507827</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.06068703166881882</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0698574412203079</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0615182363493074</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06968586552064684</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0749999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07499999999999958</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.07499999999999957</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>0.1497093017181535</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.04795024971832199</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.05980787831601261</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.04244412069970852</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.001758497264556451</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.06748865932539691</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>工作天
+Working Days</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>排線數
+Lines</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.22222222222222</v>
+      </c>
+      <c r="M13" t="n">
+        <v>14.375</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.33333333333333</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20</v>
+      </c>
+      <c r="X13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>換款率
+Turnover Rate</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>停工產能
+Suspend Work Capacity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>上週產能
+Last Week Plan Capacity</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>15652.93667</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13981.21333</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17679.99167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16774.64583</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15372.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20675.33833</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16439.30333</v>
+      </c>
+      <c r="J16" t="n">
+        <v>18983.5825</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16728.57667</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17892.3075</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15939.49667</v>
+      </c>
+      <c r="N16" t="n">
+        <v>18493.645</v>
+      </c>
+      <c r="O16" t="n">
+        <v>14581.82167</v>
+      </c>
+      <c r="P16" t="n">
+        <v>19008.53333</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="R16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="S16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12720</v>
+      </c>
+      <c r="U16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="V16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19080</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10600</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>20655.4175</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18984.1775</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>19385.79917</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>14076.3525</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>13504.395</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>11774.47167</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AB695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -59963,7 +61669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60629,7 +62335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -63413,7 +65119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
